--- a/plate3d/video/TOWER_3_HOOK.xlsx
+++ b/plate3d/video/TOWER_3_HOOK.xlsx
@@ -2061,7 +2061,7 @@
         <v>30000</v>
       </c>
       <c r="D19" s="8">
-        <v>36000</v>
+        <v>5000</v>
       </c>
       <c r="H19" s="9">
         <f>=PARAM!$J$12+1880</f>
@@ -2069,11 +2069,11 @@
       </c>
       <c r="I19" s="9">
         <f>=PARAM!$H$19-PARAM!$D$19</f>
-        <v>4020</v>
+        <v>35020</v>
       </c>
       <c r="J19" s="9">
         <f>=PARAM!$I$19-1910</f>
-        <v>2110</v>
+        <v>33110</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="K305" s="18">
         <f>=PARAM!$D$19</f>
-        <v>36000</v>
+        <v>5000</v>
       </c>
       <c r="L305">
         <v>300</v>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="K306" s="18">
         <f>=PARAM!$D$19</f>
-        <v>36000</v>
+        <v>5000</v>
       </c>
       <c r="L306">
         <v>300</v>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="K307" s="18">
         <f>=PARAM!$D$19</f>
-        <v>36000</v>
+        <v>5000</v>
       </c>
       <c r="L307">
         <v>300</v>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="K308" s="18">
         <f>=PARAM!$D$19</f>
-        <v>36000</v>
+        <v>5000</v>
       </c>
       <c r="L308">
         <v>300</v>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="H346" s="18">
         <f>=PARAM!$I$19</f>
-        <v>4020</v>
+        <v>35020</v>
       </c>
       <c r="I346">
         <v>0</v>
